--- a/analise_eua/energia_eletrica/oklo/oklo_indicators.xlsx
+++ b/analise_eua/energia_eletrica/oklo/oklo_indicators.xlsx
@@ -1,129 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="indicators_10k" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicators_10k" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicators_10q" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>P/L Damodaran</t>
-  </si>
-  <si>
-    <t>P/L</t>
-  </si>
-  <si>
-    <t>L/P</t>
-  </si>
-  <si>
-    <t>EBITDA</t>
-  </si>
-  <si>
-    <t>Margem Líquida</t>
-  </si>
-  <si>
-    <t>P/VPA</t>
-  </si>
-  <si>
-    <t>Valor de Mercado</t>
-  </si>
-  <si>
-    <t>Dívida Bruta</t>
-  </si>
-  <si>
-    <t>Caixa e Equivalentes</t>
-  </si>
-  <si>
-    <t>Dívida Líquida</t>
-  </si>
-  <si>
-    <t>Dívida Líquida/EBITDA</t>
-  </si>
-  <si>
-    <t>Dívida Líquida/PL</t>
-  </si>
-  <si>
-    <t>EV/EBITDA</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>ROIC</t>
-  </si>
-  <si>
-    <t>FCO</t>
-  </si>
-  <si>
-    <t>FCI</t>
-  </si>
-  <si>
-    <t>FCF</t>
-  </si>
-  <si>
-    <t>Free Cash Flow</t>
-  </si>
-  <si>
-    <t>Capex</t>
-  </si>
-  <si>
-    <t>Net Capex</t>
-  </si>
-  <si>
-    <t>R&amp;D</t>
-  </si>
-  <si>
-    <t>Adj Net Capex</t>
-  </si>
-  <si>
-    <t>Working Capital</t>
-  </si>
-  <si>
-    <t>Reinvestment Rate</t>
-  </si>
-  <si>
-    <t>FCFE</t>
-  </si>
-  <si>
-    <t>FCFF</t>
-  </si>
-  <si>
-    <t>-inf</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -138,35 +50,96 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -454,266 +427,561 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AB3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:28">
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>P/L Damodaran</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>P/L</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>L/P</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Margem Líquida</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P/VPA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor de Mercado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Bruta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Caixa e Equivalentes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida/EBITDA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida/PL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ROIC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>FCO</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FCI</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FCF</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Net Capex</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Adj Net Capex</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Reinvestment Rate</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>FCFE</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>FCFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-99.39</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
+      <c r="D2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>522</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10502203374</v>
+      </c>
+      <c r="I2" t="n">
+        <v>546</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1227971</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1227425</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2351.39</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="N2" t="n">
+        <v>22470.55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-82174</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-489679</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1263166</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-115379</v>
+      </c>
+      <c r="U2" t="n">
+        <v>33205</v>
+      </c>
+      <c r="V2" t="n">
+        <v>32683</v>
+      </c>
+      <c r="W2" t="n">
+        <v>58852</v>
+      </c>
+      <c r="X2" t="n">
+        <v>91535</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1228223</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-960.4100000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-149160</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-43497</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
-      <c r="A2" s="1">
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>-0.03</v>
-      </c>
-      <c r="C2">
+      <c r="B3" t="n">
+        <v>-28.52</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>-3505.75</v>
-      </c>
-      <c r="E2">
+      <c r="D3" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="E3" t="n">
         <v>268</v>
       </c>
-      <c r="F2">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>0.01</v>
-      </c>
-      <c r="H2">
-        <v>2099859.3</v>
-      </c>
-      <c r="I2">
+      <c r="G3" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2099859575.99</v>
+      </c>
+      <c r="I3" t="n">
         <v>543</v>
       </c>
-      <c r="J2">
+      <c r="J3" t="n">
         <v>227814</v>
       </c>
-      <c r="K2">
+      <c r="K3" t="n">
         <v>-227271</v>
       </c>
-      <c r="L2">
+      <c r="L3" t="n">
         <v>-848.03</v>
       </c>
-      <c r="M2">
+      <c r="M3" t="n">
         <v>-0.91</v>
       </c>
-      <c r="N2">
-        <v>855.86</v>
-      </c>
-      <c r="O2">
+      <c r="N3" t="n">
+        <v>8683.32</v>
+      </c>
+      <c r="O3" t="n">
         <v>-29.35</v>
       </c>
-      <c r="P2">
+      <c r="P3" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q2">
+      <c r="Q3" t="n">
         <v>-38390</v>
       </c>
-      <c r="R2">
+      <c r="R3" t="n">
         <v>-175774</v>
       </c>
-      <c r="S2">
+      <c r="S3" t="n">
         <v>301428</v>
       </c>
-      <c r="T2">
+      <c r="T3" t="n">
         <v>-38742</v>
       </c>
-      <c r="U2">
+      <c r="U3" t="n">
         <v>352</v>
       </c>
-      <c r="V2">
+      <c r="V3" t="n">
         <v>84</v>
       </c>
-      <c r="W2">
+      <c r="W3" t="n">
         <v>26711</v>
       </c>
-      <c r="X2">
+      <c r="X3" t="n">
         <v>26795</v>
       </c>
-      <c r="Y2">
+      <c r="Y3" t="n">
         <v>226603</v>
       </c>
-      <c r="Z2">
+      <c r="Z3" t="n">
         <v>725.33</v>
       </c>
-      <c r="AA2">
-        <v>-89628</v>
-      </c>
-      <c r="AB2">
+      <c r="AA3" t="n">
+        <v>-78570</v>
+      </c>
+      <c r="AB3" t="n">
         <v>-4954</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
-      <c r="A3" s="1">
-        <v>2023</v>
-      </c>
-      <c r="B3">
-        <v>-0.02</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>-4422.54</v>
-      </c>
-      <c r="E3">
-        <v>75</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>727478.4</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>9868</v>
-      </c>
-      <c r="K3">
-        <v>-9868</v>
-      </c>
-      <c r="L3">
-        <v>-131.57</v>
-      </c>
-      <c r="M3">
-        <v>0.29</v>
-      </c>
-      <c r="N3">
-        <v>141.27</v>
-      </c>
-      <c r="O3">
-        <v>93.63</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-15998</v>
-      </c>
-      <c r="R3">
-        <v>-83</v>
-      </c>
-      <c r="S3">
-        <v>16295</v>
-      </c>
-      <c r="T3">
-        <v>-16081</v>
-      </c>
-      <c r="U3">
-        <v>83</v>
-      </c>
-      <c r="V3">
-        <v>8</v>
-      </c>
-      <c r="W3">
-        <v>9763</v>
-      </c>
-      <c r="X3">
-        <v>9771</v>
-      </c>
-      <c r="Y3">
-        <v>10995</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3">
-        <v>-33719</v>
-      </c>
-      <c r="AB3">
-        <v>1598</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>P/L Damodaran</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>P/L</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>L/P</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Margem Líquida</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P/VPA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor de Mercado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Bruta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Caixa e Equivalentes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida/EBITDA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida Líquida/PL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ROIC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>FCO</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FCI</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FCF</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Net Capex</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Adj Net Capex</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Reinvestment Rate</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>FCFE</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>FCFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-255.46</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="E2" t="n">
+        <v>163</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8446850490.130868</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2620</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2208609</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2205989</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-4115.65</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="N2" t="n">
+        <v>19874.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-17867</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-359034</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1182559</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-50677</v>
+      </c>
+      <c r="U2" t="n">
+        <v>32810</v>
+      </c>
+      <c r="V2" t="n">
+        <v>39429</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27049</v>
+      </c>
+      <c r="X2" t="n">
+        <v>100737</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2188522</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-34404.76</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-137124</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-39842</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/analise_eua/energia_eletrica/oklo/oklo_indicators.xlsx
+++ b/analise_eua/energia_eletrica/oklo/oklo_indicators.xlsx
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,88 +897,174 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="B2" t="n">
-        <v>-255.46</v>
+        <v>-190</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72853</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-4011.24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9221823383.996523</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3259</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2465158</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2461899</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-62.14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-47592</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-553697</v>
+      </c>
+      <c r="S2" t="n">
+        <v>668790</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-115947</v>
+      </c>
+      <c r="U2" t="n">
+        <v>68355</v>
+      </c>
+      <c r="V2" t="n">
+        <v>106339</v>
+      </c>
+      <c r="W2" t="n">
+        <v>39474</v>
+      </c>
+      <c r="X2" t="n">
+        <v>199275</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2468892</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-114.23</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-257604</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-321873</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-255.46</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>-0.89</v>
       </c>
-      <c r="E2" t="n">
-        <v>163</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E3" t="n">
+        <v>-51086</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>3.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>8446850490.130868</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>2620</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J3" t="n">
         <v>2208609</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>-2205989</v>
       </c>
-      <c r="L2" t="n">
-        <v>-4115.65</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="L3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M3" t="n">
         <v>-0.84</v>
       </c>
-      <c r="N2" t="n">
-        <v>19874.7</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="N3" t="n">
+        <v>-80.15000000000001</v>
+      </c>
+      <c r="O3" t="n">
         <v>-3.69</v>
       </c>
-      <c r="P2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="P3" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-17867</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>-359034</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S3" t="n">
         <v>1182559</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T3" t="n">
         <v>-50677</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>32810</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V3" t="n">
         <v>39429</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W3" t="n">
         <v>27049</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X3" t="n">
         <v>100737</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y3" t="n">
         <v>2188522</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-34404.76</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="Z3" t="n">
+        <v>-75.63</v>
+      </c>
+      <c r="AA3" t="n">
         <v>-137124</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-39842</v>
+      <c r="AB3" t="n">
+        <v>-173289</v>
       </c>
     </row>
   </sheetData>
